--- a/artfynd/A 47549-2024 artfynd.xlsx
+++ b/artfynd/A 47549-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121452972</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47549-2024 artfynd.xlsx
+++ b/artfynd/A 47549-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121452972</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47549-2024 artfynd.xlsx
+++ b/artfynd/A 47549-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121452972</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47549-2024 artfynd.xlsx
+++ b/artfynd/A 47549-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121452972</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47549-2024 artfynd.xlsx
+++ b/artfynd/A 47549-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121452972</v>
       </c>
       <c r="B2" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
